--- a/SGC-CKN/Excel/a1ca601d-fdf4-4aba-a956-8d7d359b560d_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-113_D800_28-03-2026.xlsx
+++ b/SGC-CKN/Excel/a1ca601d-fdf4-4aba-a956-8d7d359b560d_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-113_D800_28-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
   <si>
     <t>Dự án</t>
   </si>
@@ -106,7 +106,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">17:10
@@ -116,7 +116,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">17:35
@@ -136,7 +136,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">21:35
@@ -146,7 +146,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">22:05
@@ -156,21 +156,24 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01:52
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23:52
 27/03/2026</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">02:35
 28/03/2026</t>
+  </si>
+  <si>
+    <t>NT chạm sỏi tại cao độ -35,15</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1369,13 +1372,13 @@
         <v>-39</v>
       </c>
       <c r="H17" s="26">
-        <v>3.78</v>
+        <v>1.78</v>
       </c>
       <c r="I17" s="26">
         <v>12.7</v>
       </c>
-      <c r="J17" s="19">
-        <v>3.36</v>
+      <c r="J17" s="8">
+        <v>7.12</v>
       </c>
       <c r="K17" s="27" t="s">
         <v>28</v>
@@ -1404,21 +1407,21 @@
         <v>-44.35</v>
       </c>
       <c r="H18" s="29">
-        <v>0.72</v>
+        <v>2.72</v>
       </c>
       <c r="I18" s="29">
         <v>5.35</v>
       </c>
-      <c r="J18" s="8">
-        <v>7.47</v>
+      <c r="J18" s="19">
+        <v>1.97</v>
       </c>
       <c r="K18" s="30" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
@@ -1524,31 +1527,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1745,13 +1748,13 @@
         <v>-39</v>
       </c>
       <c r="G8" s="26">
-        <v>3.78</v>
+        <v>1.78</v>
       </c>
       <c r="H8" s="26">
         <v>12.7</v>
       </c>
-      <c r="I8" s="19">
-        <v>3.36</v>
+      <c r="I8" s="8">
+        <v>7.12</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1774,18 +1777,18 @@
         <v>-44.35</v>
       </c>
       <c r="G9" s="29">
-        <v>0.72</v>
+        <v>2.72</v>
       </c>
       <c r="H9" s="29">
         <v>5.35</v>
       </c>
-      <c r="I9" s="8">
-        <v>7.47</v>
+      <c r="I9" s="19">
+        <v>1.97</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>28</v>
